--- a/research/traditional_assets/database/data/iceland/iceland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.311</v>
+        <v>0.322</v>
       </c>
       <c r="E2">
-        <v>0.643</v>
+        <v>0.272</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,19 +606,19 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>69.09999999999999</v>
+        <v>40.7</v>
       </c>
       <c r="L2">
-        <v>0.496764917325665</v>
+        <v>0.2928057553956835</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>29.1</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04560413728255759</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.714987714987715</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,58 +630,61 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>29.1</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>95.59999999999999</v>
+        <v>153.5</v>
       </c>
       <c r="V2">
-        <v>0.09697707445729356</v>
+        <v>0.2405579062842814</v>
       </c>
       <c r="W2">
-        <v>0.5381619937694704</v>
+        <v>0.06989524300188907</v>
       </c>
       <c r="X2">
-        <v>0.02760739963024673</v>
+        <v>0.05732104932163401</v>
       </c>
       <c r="Y2">
-        <v>0.5105545941392237</v>
+        <v>0.01257419368025506</v>
       </c>
       <c r="Z2">
-        <v>0.9837340876944837</v>
+        <v>0.2145061728395062</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02670709393274175</v>
+        <v>0.05256281436539392</v>
       </c>
       <c r="AC2">
-        <v>-0.02670709393274175</v>
+        <v>-0.05256281436539392</v>
       </c>
       <c r="AD2">
-        <v>393.1</v>
+        <v>471.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>393.1</v>
+        <v>471.5</v>
       </c>
       <c r="AG2">
-        <v>297.5</v>
+        <v>318</v>
       </c>
       <c r="AH2">
-        <v>0.2850823119878164</v>
+        <v>0.4249279019466475</v>
       </c>
       <c r="AI2">
-        <v>0.4031381396779817</v>
+        <v>0.4633451257861635</v>
       </c>
       <c r="AJ2">
-        <v>0.2318242032260578</v>
+        <v>0.3326011923438971</v>
       </c>
       <c r="AK2">
-        <v>0.3382603752131893</v>
+        <v>0.3680129614627937</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.311</v>
+        <v>0.322</v>
       </c>
       <c r="E3">
-        <v>0.643</v>
+        <v>0.272</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,19 +728,19 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>69.09999999999999</v>
+        <v>40.7</v>
       </c>
       <c r="L3">
-        <v>0.496764917325665</v>
+        <v>0.2928057553956835</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>29.1</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04560413728255759</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.714987714987715</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,58 +752,61 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>29.1</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>95.59999999999999</v>
+        <v>153.5</v>
       </c>
       <c r="V3">
-        <v>0.09697707445729356</v>
+        <v>0.2405579062842814</v>
       </c>
       <c r="W3">
-        <v>0.5381619937694704</v>
+        <v>0.06989524300188907</v>
       </c>
       <c r="X3">
-        <v>0.02760739963024673</v>
+        <v>0.05732104932163401</v>
       </c>
       <c r="Y3">
-        <v>0.5105545941392237</v>
+        <v>0.01257419368025506</v>
       </c>
       <c r="Z3">
-        <v>0.9837340876944837</v>
+        <v>0.2145061728395062</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.02670709393274175</v>
+        <v>0.05256281436539392</v>
       </c>
       <c r="AC3">
-        <v>-0.02670709393274175</v>
+        <v>-0.05256281436539392</v>
       </c>
       <c r="AD3">
-        <v>393.1</v>
+        <v>471.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>393.1</v>
+        <v>471.5</v>
       </c>
       <c r="AG3">
-        <v>297.5</v>
+        <v>318</v>
       </c>
       <c r="AH3">
-        <v>0.2850823119878164</v>
+        <v>0.4249279019466475</v>
       </c>
       <c r="AI3">
-        <v>0.4031381396779817</v>
+        <v>0.4633451257861635</v>
       </c>
       <c r="AJ3">
-        <v>0.2318242032260578</v>
+        <v>0.3326011923438971</v>
       </c>
       <c r="AK3">
-        <v>0.3382603752131893</v>
+        <v>0.3680129614627937</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/iceland/iceland_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_financial_svcs_non_bank_insurance.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.322</v>
+        <v>0.283</v>
       </c>
       <c r="E2">
-        <v>0.272</v>
+        <v>0.158</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>40.7</v>
+        <v>30.2</v>
       </c>
       <c r="L2">
-        <v>0.2928057553956835</v>
+        <v>0.2062841530054645</v>
       </c>
       <c r="M2">
-        <v>29.1</v>
+        <v>21.19</v>
       </c>
       <c r="N2">
-        <v>0.04560413728255759</v>
+        <v>0.03522859517871987</v>
       </c>
       <c r="O2">
-        <v>0.714987714987715</v>
+        <v>0.7016556291390729</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.02310889443059019</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.4602649006622517</v>
       </c>
       <c r="S2">
-        <v>29.1</v>
+        <v>7.290000000000001</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>0.3440302029259085</v>
       </c>
       <c r="U2">
-        <v>153.5</v>
+        <v>241.1</v>
       </c>
       <c r="V2">
-        <v>0.2405579062842814</v>
+        <v>0.400831255195345</v>
       </c>
       <c r="W2">
-        <v>0.06989524300188907</v>
+        <v>0.05536205316223648</v>
       </c>
       <c r="X2">
-        <v>0.05732104932163401</v>
+        <v>0.0627093008214293</v>
       </c>
       <c r="Y2">
-        <v>0.01257419368025506</v>
+        <v>-0.00734724765919282</v>
       </c>
       <c r="Z2">
-        <v>0.2145061728395062</v>
+        <v>0.2158973602713464</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05256281436539392</v>
+        <v>0.05363406935024333</v>
       </c>
       <c r="AC2">
-        <v>-0.05256281436539392</v>
+        <v>-0.05363406935024333</v>
       </c>
       <c r="AD2">
-        <v>471.5</v>
+        <v>533.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>471.5</v>
+        <v>533.9</v>
       </c>
       <c r="AG2">
-        <v>318</v>
+        <v>292.8</v>
       </c>
       <c r="AH2">
-        <v>0.4249279019466475</v>
+        <v>0.4702307556808173</v>
       </c>
       <c r="AI2">
-        <v>0.4633451257861635</v>
+        <v>0.4787482065997131</v>
       </c>
       <c r="AJ2">
-        <v>0.3326011923438971</v>
+        <v>0.3274069104327407</v>
       </c>
       <c r="AK2">
-        <v>0.3680129614627937</v>
+        <v>0.33497311520421</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.322</v>
+        <v>0.283</v>
       </c>
       <c r="E3">
-        <v>0.272</v>
+        <v>0.158</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>40.7</v>
+        <v>30.2</v>
       </c>
       <c r="L3">
-        <v>0.2928057553956835</v>
+        <v>0.2062841530054645</v>
       </c>
       <c r="M3">
-        <v>29.1</v>
+        <v>21.19</v>
       </c>
       <c r="N3">
-        <v>0.04560413728255759</v>
+        <v>0.03522859517871987</v>
       </c>
       <c r="O3">
-        <v>0.714987714987715</v>
+        <v>0.7016556291390729</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>13.9</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02310889443059019</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.4602649006622517</v>
       </c>
       <c r="S3">
-        <v>29.1</v>
+        <v>7.290000000000001</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.3440302029259085</v>
       </c>
       <c r="U3">
-        <v>153.5</v>
+        <v>241.1</v>
       </c>
       <c r="V3">
-        <v>0.2405579062842814</v>
+        <v>0.400831255195345</v>
       </c>
       <c r="W3">
-        <v>0.06989524300188907</v>
+        <v>0.05536205316223648</v>
       </c>
       <c r="X3">
-        <v>0.05732104932163401</v>
+        <v>0.0627093008214293</v>
       </c>
       <c r="Y3">
-        <v>0.01257419368025506</v>
+        <v>-0.00734724765919282</v>
       </c>
       <c r="Z3">
-        <v>0.2145061728395062</v>
+        <v>0.2158973602713464</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05256281436539392</v>
+        <v>0.05363406935024333</v>
       </c>
       <c r="AC3">
-        <v>-0.05256281436539392</v>
+        <v>-0.05363406935024333</v>
       </c>
       <c r="AD3">
-        <v>471.5</v>
+        <v>533.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>471.5</v>
+        <v>533.9</v>
       </c>
       <c r="AG3">
-        <v>318</v>
+        <v>292.8</v>
       </c>
       <c r="AH3">
-        <v>0.4249279019466475</v>
+        <v>0.4702307556808173</v>
       </c>
       <c r="AI3">
-        <v>0.4633451257861635</v>
+        <v>0.4787482065997131</v>
       </c>
       <c r="AJ3">
-        <v>0.3326011923438971</v>
+        <v>0.3274069104327407</v>
       </c>
       <c r="AK3">
-        <v>0.3680129614627937</v>
+        <v>0.33497311520421</v>
       </c>
       <c r="AL3">
         <v>0</v>
